--- a/신고신저가_20260810.xlsx
+++ b/신고신저가_20260810.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,64 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 7월 미 고용 마이너스(-2.3만, 컨센 +8.3만)로 금리 인상 리스크 후퇴 — 실적 확인된 성장주로 매수 집중, 방어·유틸리티는 소외되는 차별화 국면.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/7): 나스닥 +1.30%·S&amp;P500 +0.62%·다우 +0.28%, 10년물 4.64%(-3bp). Technology Services 신고22/신저1(순강도 +21, 12MF PER 23.2)·Health Technology 13/0(18.8)이 주도. 아틀라시안 +35%·트윌로 +25%·에어비앤비 +17% 모두 2분기 서프라이즈. 반대편은 유틸리티(순강도 -6, 신저 6종, XLU 1M -3.4%)와 에너지(XLE -1.1%·주간 -3.4%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/7): 1분기 결산 랠리 — 의약품 ETF +2.8%·철강비철 +2.2%·에너지자원 +2.1%. 혼다(연간 +53.8% 상향)·브리지스톤(순익 79%↑ 사상최대)·산리오(5기 연속 최고)·반다이남코가 신고가. 유일한 약세는 건설·자재 -1.9%로 오바야시·카지마 신저가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 中·홍콩(8/7): 상해종합 +1.02%·CSI300 +0.93%·항셍 +0.54%·항셍테크 +0.78%. 의약 ETF +4.5%로 A주 최강 — 우시앱텍 상반기 순익 29%↑ 서프라이즈에 캉룽화청·우시바이오·베이진이 홍콩·A주 양쪽에서 동반 신고가. 유색금속 +3.5%(콩고 구리정광 수출금지, 시부쾅예 +8.4%), 반도체 +3.4%. 은행만 -0.9%로 성장주 로테이션.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①인상 리스크 후퇴가 인하 기대로 넘어가는지(다음 CPI) ②CXO 랠리가 미 Health Technology 신고 13종과 이어지는 글로벌 헬스케어 테마인지 ③금리 내렸는데도 미 유틸리티 신저 6종 — 금리가 아닌 구조 요인일 가능성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 전 시장 2026-08-07(금) 마감 확정치. 미장은 한국시간 8월 8일 새벽 마감분으로, 주말 공백 뒤 오늘 아침 처음 확인하는 세션. 닛케이 지수 등락은 소스 미확보라 일본은 섹터ETF 기준으로 기술.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +771,19 @@
       <c r="C2" t="n">
         <v>7757.64</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>3.58</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>2.84</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>5.73</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>13.32</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +809,19 @@
       <c r="C3" t="n">
         <v>26690.62</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>5.19</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>1.85</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>3.43</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>14.84</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +847,19 @@
       <c r="C4" t="n">
         <v>6258.77</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>-5.1</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>-13.63</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-16.44</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>48.52</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +885,19 @@
       <c r="C5" t="n">
         <v>65606.71000000001</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-0.12</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>1.93</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>-1.81</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>5.11</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>30.33</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +923,19 @@
       <c r="C6" t="n">
         <v>3940.04</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>1.02</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>2.81</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>-2.39</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-6.75</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-0.73</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +961,19 @@
       <c r="C7" t="n">
         <v>4694.44</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>2.32</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-3.73</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>1.39</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +999,19 @@
       <c r="C8" t="n">
         <v>25668.03</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>-0.84</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>6.82</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1037,19 @@
       <c r="C9" t="n">
         <v>4858.29</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>2.68</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-5.13</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-11.92</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1168,7 @@
       <c r="F2" t="n">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1209,7 @@
       <c r="F3" t="n">
         <v>13</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1250,7 @@
       <c r="F4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1291,7 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1332,7 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1373,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1414,7 @@
       <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1455,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1496,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1537,7 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1578,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1619,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1660,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1701,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1678,7 +1740,7 @@
       <c r="F16" t="n">
         <v>-1</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1719,7 +1781,7 @@
       <c r="F17" t="n">
         <v>-3</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1760,7 +1822,7 @@
       <c r="F18" t="n">
         <v>-6</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1986,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1963,7 +2025,7 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2066,7 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2105,7 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2084,7 +2146,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2123,7 +2185,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2162,7 +2224,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2201,7 +2263,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2242,7 +2304,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2281,7 +2343,7 @@
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2320,7 +2382,7 @@
       <c r="F32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2359,7 +2421,7 @@
       <c r="F33" t="n">
         <v>-1</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2636,7 +2698,7 @@
       <c r="F40" t="n">
         <v>4</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2677,7 +2739,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2716,7 +2778,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2757,7 +2819,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2798,7 +2860,7 @@
       <c r="F44" t="n">
         <v>-1</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3358,7 +3420,7 @@
       <c r="F58" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3399,7 +3461,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3440,7 +3502,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3479,7 +3541,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -4062,30 +4124,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4106,90 +4169,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4211,58 +4279,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>+1.4%·주간 +7.2%, YTD +30.9% 1위. 아틀라시안·트윌로 실적 서프라이즈로 SW 신고가 22종 주도</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4282,58 +4355,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>+0.7%, Health Technology 신고 13/신저 0. 나테라·할로자임 가이던스 상향이 견인</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4353,58 +4431,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>-0.4%로 당일 약세지만 신고 9/신저 0 유지, 금리 하락에 마진 우려 추정</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4424,58 +4507,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>+1.5% 당일 최강, 에어비앤비 +17%·인스타카트 +11% 실적 서프라이즈</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4495,58 +4583,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>+0.1% 보합, YTD -4.9%로 11개 섹터 중 최하위 지속</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4566,58 +4659,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>+0.2%, 산업서비스 신저 3종으로 섹터 내부 온도차</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4637,58 +4735,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>보합(0.0%), 신고 1/신저 0으로 방향성 부재</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4708,58 +4811,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>-1.1%·주간 -3.4%로 당일 최약, 다만 YTD +30.4%는 여전히 2위</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4779,58 +4887,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>+0.5% 반등에도 신저가 6종·1M -3.4%, 금리 아닌 구조 약세로 추정</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4850,58 +4963,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>+1.3%, 구리 강세 수혜 추정이나 신고 2/신저 1로 혼조</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4921,58 +5039,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>+0.4%, 금리 하락에 소폭 반등(추정), 신고·신저 모두 없음</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4992,58 +5115,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5063,58 +5187,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5134,58 +5259,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-6.9</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5205,58 +5331,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5276,58 +5403,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>13</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5347,58 +5475,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>9.1</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5418,58 +5547,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-16</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5489,58 +5619,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>7</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5560,58 +5691,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5631,58 +5763,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5702,58 +5835,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5773,58 +5907,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>14</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5844,58 +5979,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5915,58 +6051,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5986,58 +6123,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>45.9</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6057,58 +6195,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6128,58 +6267,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6199,58 +6339,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6270,58 +6411,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6341,56 +6483,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-11.6</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6408,58 +6551,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>반도체 +3.4%·주간 +9.2%, YTD +48.0%로 A주 1위 — 진왕전자 PCB 상한가</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-26.4</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6479,58 +6627,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>테크 +2.8%·주간 +8.9%, AI인프라 체인 전반으로 매수 확산</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-18.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6550,58 +6703,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>5G통신 +2.9%·주간 +13.4%로 주간 최강, 광모듈·AI연산 기대</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6621,56 +6779,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>신에너지차 +1.3%, 3M -22.4% 낙폭과대 반등 수준으로 추정</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-22.4</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-11.2</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6688,58 +6851,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>방산 +1.7% 반등이나 YTD -16.0%로 최하위권 유지</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-22.2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-16</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6759,56 +6927,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>태양광 +2.5% 반등, 3M -22.9%라 추세 전환은 미확인</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-22.9</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-10</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6826,58 +6999,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>백주 +0.2% 보합, 1M +13.6% 반등 뒤 숨고르기</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>13.6</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-18.8</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6897,58 +7075,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>은행 -0.9%·주간 -4.5%로 A주 유일 약세, 성장주 로테이션</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6968,58 +7151,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>유색금속 +3.5%·주간 +10.8%, 콩고 구리정광 수출금지에 시부쾅예 +8.4%</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-10.1</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7039,58 +7227,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>부동산 보합(0.0%), YTD -19.5%로 A주 최하위 지속</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-20</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-19.5</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7110,58 +7303,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>증권 보합(0.0%), 지수 +1.0% 상승에도 무반응</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.5</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7181,58 +7379,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>의약 +4.5% A주 최강, 우시앱텍 상반기 순익 29%↑에 CXO 동반 급등</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7252,58 +7455,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>소비 +0.4%, 주간 -3.6%로 내수 부진 지속</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7315,7 +7523,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.9"/>
@@ -7327,7 +7535,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-4.5"/>
@@ -7339,7 +7547,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-26.4"/>
@@ -7351,7 +7559,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-22.9"/>
@@ -7363,7 +7571,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-19.5"/>
@@ -7375,7 +7583,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7387,7 +7595,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7399,7 +7607,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7411,7 +7619,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7423,7 +7631,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7435,7 +7643,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7549,7 +7757,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7598,15 +7806,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7648,15 +7856,15 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7700,10 +7908,10 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7750,15 +7958,15 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7798,15 +8006,15 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7852,10 +8060,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7904,19 +8112,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 엔브리지(캐나다 에너지 파이프라인): 개별 뉴스 없음, 에너지 섹터 약세(추정)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7962,15 +8170,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8018,10 +8226,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8070,10 +8278,10 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8122,15 +8330,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8172,10 +8380,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8224,15 +8432,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8276,15 +8484,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8332,10 +8540,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8384,15 +8592,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8436,15 +8644,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8492,10 +8700,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8548,10 +8756,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8600,15 +8808,15 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8652,10 +8860,10 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8704,15 +8912,15 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8756,15 +8964,15 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8808,15 +9016,15 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8860,15 +9068,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8912,15 +9120,15 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8964,10 +9172,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9016,15 +9224,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9068,15 +9276,15 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9120,15 +9328,15 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9168,10 +9376,10 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9220,15 +9428,15 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9274,15 +9482,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9326,15 +9534,15 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9378,15 +9586,15 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9430,10 +9638,10 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9484,19 +9692,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr">
+      <c r="N38" s="10" t="inlineStr">
         <is>
           <t>(전일) 벤딩스푼스(앱 인수·운영 이탈리아 테크): +16.8% 급등, 촉매 미확인(상장 초기 변동성 추정)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9542,10 +9750,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9592,10 +9800,10 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9648,19 +9856,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>(전일) 샤크닌자(소형가전): 2분기 서프라이즈·연간 가이던스 상향으로 +8.3%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9704,10 +9912,10 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9760,15 +9968,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9814,15 +10022,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9866,15 +10074,15 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9918,10 +10126,10 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9970,15 +10178,15 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10020,10 +10228,10 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10074,10 +10282,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10124,19 +10332,19 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr">
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>(전일) 유니티소프트웨어(게임엔진·3D툴): Q2 실적(8/5) 기대·전략매출 35% 성장 확인, 7/31 급락분 반등에 나스닥 강세 수혜</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10180,15 +10388,15 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10232,15 +10440,15 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10280,15 +10488,15 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10332,10 +10540,10 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10384,10 +10592,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10436,15 +10644,15 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10490,15 +10698,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N57" s="7" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10540,10 +10748,10 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10596,10 +10804,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10652,14 +10860,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N60" s="7" t="inlineStr">
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>(전일) RB글로벌(산업장비 경매 마켓플레이스): 실적 실망으로 -13.9%, 신저가</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10708,15 +10916,15 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10764,15 +10972,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10816,10 +11024,10 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10872,15 +11080,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10924,10 +11132,10 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" s="7" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10976,10 +11184,10 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11028,15 +11236,15 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11080,10 +11288,10 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" s="7" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11132,10 +11340,10 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11184,10 +11392,10 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11232,10 +11440,10 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11284,15 +11492,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="7" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11336,10 +11544,10 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11388,10 +11596,10 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11442,15 +11650,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="7" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11494,10 +11702,10 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11546,15 +11754,15 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11596,15 +11804,15 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11648,10 +11856,10 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11698,14 +11906,14 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="7" t="inlineStr">
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>(전일) 다비타(신장투석 체인): 2분기 EPS 상회에도 가이던스 우려로 -17%, 신저가</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11758,15 +11966,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11806,15 +12014,15 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11858,15 +12066,15 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="7" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11910,10 +12118,10 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11962,7 +12170,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N85" s="7" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N85"/>
@@ -12068,7 +12276,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12115,15 +12323,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12169,15 +12377,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12223,15 +12431,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12273,15 +12481,15 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12327,10 +12535,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12383,14 +12591,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 일본제철(고로 철강): 1분기 실적 상향수정으로 +4%, 철강·비철 섹터 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12437,10 +12645,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12491,15 +12699,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12541,10 +12749,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12597,15 +12805,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12647,10 +12855,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12699,15 +12907,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12749,15 +12957,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12799,10 +13007,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12855,10 +13063,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12903,15 +13111,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12955,10 +13163,10 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13007,15 +13215,15 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13057,7 +13265,7 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N20"/>
@@ -13163,12 +13371,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13214,15 +13422,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13270,15 +13478,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13322,10 +13530,10 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13378,14 +13586,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 촹커실업(밀워키·라이오비 전동공구): 상반기 순이익 +17.5%·배당 20%↑·5억달러 자사주로 +8.1%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13438,19 +13646,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 야오밍바이오(바이오의약 CDMO): 야오밍캉더 실적발 위탁개발 업종 훈풍에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13496,15 +13704,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13550,15 +13758,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13602,10 +13810,10 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13656,19 +13864,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 캐세이퍼시픽(홍콩 국적 항공사): 상반기 순이익 65~75% 급증 전망 공시로 강세</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13714,15 +13922,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13766,15 +13974,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13814,7 +14022,7 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N13"/>
@@ -13920,12 +14128,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13971,10 +14179,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14023,10 +14231,10 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14077,10 +14285,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14131,19 +14339,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 시부쾅예(구리·아연·몰리브덴 광산): 상반기 순이익 +123% 사상 최고, 유색금속 강세로 +7.4%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14189,15 +14397,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14243,15 +14451,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14299,7 +14507,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N8"/>

--- a/신고신저가_20260810.xlsx
+++ b/신고신저가_20260810.xlsx
@@ -8226,7 +8226,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>에어비앤비(숙박공유 플랫폼): 2분기 서프라이즈·GBV 16%↑, 3분기·연간 매출 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -9016,7 +9020,11 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="10" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>엑셀에너지(미 중서부 전력): 특별한 뉴스 없음, 금리 하락에 소폭 반등했으나 52주 신저</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -9068,7 +9076,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="10" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>나테라(암·유전자 진단검사): 2분기 매출 컨센 대폭 상회, 연간 가이던스 상향·검사량 기록</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -9376,7 +9388,11 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="10" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>아틀라시안(협업SW Jira·Confluence): 2분기 매출 28%↑·클라우드 31% 가속, Rovo AI 견인</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -9482,7 +9498,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N34" s="10" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>트윌로(클라우드 통신API): 2분기 매출·EPS 서프라이즈, 3분기 가이던스·FCF 전망 상향</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -9586,7 +9606,11 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="10" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>WEC에너지(위스콘신 전력·가스): 특별한 뉴스 없음, 유틸리티 섹터 소외 흐름 추정</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -10022,7 +10046,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="10" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>암라이즈(시멘트·콘크리트 건자재): 2분기 EPS 원가인플레로 부진, EBITDA 가이던스 하향</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -10804,7 +10832,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="10" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>제임스하디(파이버시멘트 건축자재): FY27 1분기 EBITDA 가이던스 상회, AZEK 통합 기대</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -11132,7 +11164,11 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" s="10" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr">
+        <is>
+          <t>에메라(캐나다·미국 전력·가스 유틸리티): 2분기 조정EPS 컨센 미달로 실망 매도</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -11856,7 +11892,11 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="10" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>메이플베어(인스타카트, 식료품 배달): 2분기 매출 컨센 상회·광고 호조, 조정EBITDA 19%↑</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -11966,7 +12006,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>할로자임(약물전달 플랫폼 ENHANZE 로열티): 2분기 서프라이즈·연간 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -12431,7 +12475,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>오츠카홀딩스(제약·헬스케어): 연간 실적·배당 상향, 신장병 신약 임상 호조</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -12481,7 +12529,11 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>혼다(자동차): 1분기 순이익 2.3배, 연간 전망 53.8% 상향에 목표주가 동반 상향</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -12535,7 +12587,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>브리지스톤(타이어 제조): 상반기 순이익 79%↑ 사상 최대, 상장 이래 최고가 경신</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -12593,7 +12649,7 @@
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>(전일) 일본제철(고로 철강): 1분기 실적 상향수정으로 +4%, 철강·비철 섹터 동반 급등</t>
+          <t>일본제철(철강): 연간 실적 상향 + US스틸 수익 개선 기대로 신고가</t>
         </is>
       </c>
     </row>
@@ -12645,7 +12701,11 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>반다이남코(게임·완구 IP): 1분기 사상 최대 실적, 2분기 누계 가이던스도 상향</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -12749,7 +12809,11 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>LY코퍼레이션(야후재팬·라인): 1분기 사상 최대 실적 + 1500억엔 자사주매입</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -12855,7 +12919,11 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="10" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>카지마(종합건설): 특별한 뉴스 없음, 건설 섹터 동반 조정 추정</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -13007,7 +13075,11 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>오바야시구미(종합건설): 1분기 영업이익 98%↑에도 가이던스 유지, 차익실현 매물</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -13063,7 +13135,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="10" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>도레이(첨단소재·탄소섬유): 1분기 순이익 92.6%↑, 상반기 이익전망 13% 상향</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -13163,7 +13239,11 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="10" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>산리오(헬로키티 캐릭터 IP): 5기 연속 최고실적, 아시아 매출 급증에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -13422,7 +13502,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>우시앱텍(신약 위탁연구 CRO): 상반기 순이익 29% 증가 서프라이즈, CXO 급등 주도</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -13478,7 +13562,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>레노버(PC·서버 제조): AI서버 수주 210억달러·실적 호조로 신고가 경신</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -13530,7 +13618,11 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>베이진(신약개발 바이오텍): 실적 호조·애널리스트 상향 속 CXO 섹터 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -13648,7 +13740,7 @@
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>(전일) 야오밍바이오(바이오의약 CDMO): 야오밍캉더 실적발 위탁개발 업종 훈풍에 동반 상승</t>
+          <t>우시바이오로직스(바이오의약품 CDMO): 우시앱텍발 CXO 급등 여진으로 52주 신고</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13796,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>스와이어퍼시픽B(항공·부동산 복합기업): 상반기 순이익 43% 증가 서프라이즈</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -13810,7 +13906,11 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>완저우인터내셔널(육가공 식품): 특별한 뉴스 없음, 마진 둔화 우려 속 수급 조정 추정</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -13922,7 +14022,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="10" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>샤오펑(전기차 제조): 자율주행 표준 훈풍 속 전기차 섹터 동반 소폭 상승</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -13974,7 +14078,11 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="10" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>캉룽화청(신약 위탁연구 CRO): 우시앱텍 실적 서프라이즈로 CXO 섹터 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -14022,7 +14130,11 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>니오(전기차 제조): 중국 자율주행 표준 훈풍·7월 인도량 71% 증가로 소폭 상승</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N13"/>
@@ -14179,7 +14291,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>우시앱텍A(신약 위탁개발 CXO): 글로벌 수주잔고 급증·기술수출 호조로 섹터 동반 급등</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -14231,7 +14347,11 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>베이진A(바이오 신약): 8월 5일 발표 상반기 실적 서프라이즈, 주력 신약 매출 29%↑</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -14341,7 +14461,7 @@
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>(전일) 시부쾅예(구리·아연·몰리브덴 광산): 상반기 순이익 +123% 사상 최고, 유색금속 강세로 +7.4%</t>
+          <t>시부쾅예(비철금속·구리 채굴): 콩고 구리정광 수출금지로 구리값 사상 최고 경신</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14517,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>진왕전자(스마트폰·서버용 PCB): AI인프라용 고다층 PCB·1.6T 광모듈 기대로 2연속 상한가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -14451,7 +14575,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>루이터커지(적외선 열영상 센서): 특별한 뉴스 없음, 실적장세 이후 수급 흐름 추정</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -14507,7 +14635,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>캉룽화청A(신약 위탁개발 CXO): 상반기 중국 기술수출 2배 급증·수주잔고 25%↑</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N8"/>
